--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB319B4-1183-41FE-A4FA-1A83398BED2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BF9CB3-45AA-4B7E-850A-7502AB862661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13695" yWindow="2010" windowWidth="14730" windowHeight="13275" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="26385" windowHeight="13440" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作業部屋見取り図" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4115" uniqueCount="1472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="1481">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -4463,6 +4463,72 @@
     <t>アルミ針金（巻）</t>
     <rPh sb="3" eb="5">
       <t>ハリガネ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I-00385</t>
+  </si>
+  <si>
+    <t>交換用バックル（ジーンズ用）</t>
+  </si>
+  <si>
+    <t>気に入った革ベルトが見つかるまで保留、未使用</t>
+  </si>
+  <si>
+    <t>SZ 接眼レンズ 補助レンズ　プレート</t>
+    <rPh sb="3" eb="5">
+      <t>セツガン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I-00386</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>T-0306</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タブレットアーム　備品</t>
+    <rPh sb="9" eb="11">
+      <t>ビヒン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮）南ラック白いガラス棚</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミナミ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>シロ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>タナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮）南押入れ2段目</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ミナミ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>オシイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ダンメ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -23983,47 +24049,47 @@
     <row r="400" spans="1:11">
       <c r="A400" t="str">
         <f>IFERROR(INDEX(T項目!$A:$A,MATCH(アイテムビューア!$C400,T項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>S-003</v>
       </c>
       <c r="B400" t="str">
         <f>IFERROR(INDEX(S項目!$B:$B,MATCH(アイテムビューア!$A400,S項目!$A:$A,0)),"")</f>
-        <v/>
+        <v>南ラック</v>
       </c>
       <c r="C400" t="str">
         <f>IFERROR(INDEX(C項目!$A:$A,MATCH(アイテムビューア!$E400,C項目!$D:$D,0)),"")</f>
-        <v/>
+        <v>T-0303</v>
       </c>
       <c r="D400" t="str">
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C400,T項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E400">
+        <v>中央スチール棚</v>
+      </c>
+      <c r="E400" t="str">
         <f>アイテム項目!$A400</f>
-        <v>0</v>
+        <v>C-030304</v>
       </c>
       <c r="F400" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E400,C項目!$D:$D,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G400">
+        <v>SNOOPYミニトート・工具ケース</v>
+      </c>
+      <c r="G400" t="str">
         <f>アイテム項目!$E400</f>
-        <v>0</v>
-      </c>
-      <c r="H400">
+        <v>I-00385</v>
+      </c>
+      <c r="H400" t="str">
         <f>アイテム項目!$F400</f>
-        <v>0</v>
-      </c>
-      <c r="I400">
+        <v>交換用バックル（ジーンズ用）</v>
+      </c>
+      <c r="I400" t="str">
         <f>アイテム項目!$G400</f>
-        <v>0</v>
-      </c>
-      <c r="J400">
+        <v>雑貨</v>
+      </c>
+      <c r="J400" t="str">
         <f>アイテム項目!$H400</f>
-        <v>0</v>
-      </c>
-      <c r="K400">
+        <v>B</v>
+      </c>
+      <c r="K400" t="str">
         <f>アイテム項目!$I400</f>
-        <v>0</v>
+        <v>気に入った革ベルトが見つかるまで保留、未使用</v>
       </c>
     </row>
     <row r="401" spans="1:11">
@@ -24089,21 +24155,21 @@
         <f>IFERROR(INDEX(T項目!$E:$E,MATCH(アイテムビューア!$C402,T項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="E402">
+      <c r="E402" t="str">
         <f>アイテム項目!$A402</f>
-        <v>0</v>
+        <v>T-0306</v>
       </c>
       <c r="F402" t="str">
         <f>IFERROR(INDEX(C項目!$E:$E,MATCH(アイテムビューア!$E402,C項目!$D:$D,0)),"")</f>
         <v/>
       </c>
-      <c r="G402">
+      <c r="G402" t="str">
         <f>アイテム項目!$E402</f>
-        <v>0</v>
-      </c>
-      <c r="H402">
+        <v>I-00386</v>
+      </c>
+      <c r="H402" t="str">
         <f>アイテム項目!$F402</f>
-        <v>0</v>
+        <v>SZ 接眼レンズ 補助レンズ　プレート</v>
       </c>
       <c r="I402">
         <f>アイテム項目!$G402</f>
@@ -24147,9 +24213,9 @@
         <f>アイテム項目!$E403</f>
         <v>0</v>
       </c>
-      <c r="H403">
+      <c r="H403" t="str">
         <f>アイテム項目!$F403</f>
-        <v>0</v>
+        <v>タブレットアーム　備品</v>
       </c>
       <c r="I403">
         <f>アイテム項目!$G403</f>
@@ -32201,7 +32267,7 @@
     <col min="1" max="1" width="21.5" style="29" customWidth="1"/>
     <col min="2" max="2" width="25.125" style="29" customWidth="1"/>
     <col min="4" max="4" width="18.625" style="29" customWidth="1"/>
-    <col min="5" max="5" width="29.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.25" style="29" customWidth="1"/>
     <col min="6" max="6" width="6.625" style="29" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="29" customWidth="1"/>
   </cols>
@@ -33589,7 +33655,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:K399"/>
+  <dimension ref="A1:K403"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.625" style="29" bestFit="1" customWidth="1"/>
@@ -33598,7 +33664,7 @@
     <col min="4" max="4" width="12.625" style="29" customWidth="1"/>
     <col min="6" max="6" width="44.25" style="29" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.25" style="29" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.75" style="29" customWidth="1"/>
     <col min="9" max="9" width="12.5" style="29" customWidth="1"/>
     <col min="10" max="10" width="11.125" style="29" customWidth="1"/>
   </cols>
@@ -43033,7 +43099,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="385" spans="1:8">
+    <row r="385" spans="1:9">
       <c r="A385" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43059,7 +43125,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="386" spans="1:8">
+    <row r="386" spans="1:9">
       <c r="A386" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43085,7 +43151,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="387" spans="1:8">
+    <row r="387" spans="1:9">
       <c r="A387" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43111,7 +43177,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="388" spans="1:8">
+    <row r="388" spans="1:9">
       <c r="A388" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43137,7 +43203,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="389" spans="1:8">
+    <row r="389" spans="1:9">
       <c r="A389" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43163,7 +43229,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="390" spans="1:8">
+    <row r="390" spans="1:9">
       <c r="A390" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43189,7 +43255,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="391" spans="1:8">
+    <row r="391" spans="1:9">
       <c r="A391" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43215,7 +43281,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="392" spans="1:8">
+    <row r="392" spans="1:9">
       <c r="A392" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43241,7 +43307,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="393" spans="1:8">
+    <row r="393" spans="1:9">
       <c r="A393" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43267,7 +43333,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="394" spans="1:8">
+    <row r="394" spans="1:9">
       <c r="A394" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43293,7 +43359,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="395" spans="1:8">
+    <row r="395" spans="1:9">
       <c r="A395" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43319,7 +43385,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="396" spans="1:8">
+    <row r="396" spans="1:9">
       <c r="A396" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43345,7 +43411,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="397" spans="1:8">
+    <row r="397" spans="1:9">
       <c r="A397" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43371,7 +43437,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="398" spans="1:8">
+    <row r="398" spans="1:9">
       <c r="A398" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43397,7 +43463,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="399" spans="1:8">
+    <row r="399" spans="1:9">
       <c r="A399" s="29" t="s">
         <v>1288</v>
       </c>
@@ -43421,6 +43487,57 @@
       </c>
       <c r="H399" s="29" t="s">
         <v>1288</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9">
+      <c r="A400" s="29" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B400" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C400" s="29" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D400" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="E400" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F400" s="29" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G400" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="H400" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="I400" s="29" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6">
+      <c r="A402" s="29" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C402" s="29" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E402" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F402" s="29" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6">
+      <c r="C403" s="29" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F403" s="29" t="s">
+        <v>1478</v>
       </c>
     </row>
   </sheetData>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BF9CB3-45AA-4B7E-850A-7502AB862661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FF7776-E630-4618-9951-9F025D8D4A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="26385" windowHeight="13440" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1590" windowWidth="26385" windowHeight="13440" tabRatio="901" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作業部屋見取り図" sheetId="1" r:id="rId1"/>
@@ -26,12 +26,15 @@
     <sheet name="全体配置" sheetId="11" r:id="rId11"/>
     <sheet name="列名一覧" sheetId="12" r:id="rId12"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">アイテム項目!$A$1:$A$403</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="1481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4130" uniqueCount="1483">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -3487,9 +3490,6 @@
     <t>サイズ区分</t>
   </si>
   <si>
-    <t>C-0009</t>
-  </si>
-  <si>
     <t>N-00001</t>
   </si>
   <si>
@@ -3497,9 +3497,6 @@
   </si>
   <si>
     <t>内部未調査</t>
-  </si>
-  <si>
-    <t>C-0010</t>
   </si>
   <si>
     <t>N-00002</t>
@@ -4530,6 +4527,22 @@
     <rPh sb="7" eb="9">
       <t>ダンメ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C-010503</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C-010506</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -15483,7 +15496,7 @@
       </c>
       <c r="J213" t="str">
         <f>アイテム項目!$H213</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="K213" t="str">
         <f>アイテム項目!$I213</f>
@@ -15529,7 +15542,7 @@
       </c>
       <c r="J214" t="str">
         <f>アイテム項目!$H214</f>
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="K214" t="str">
         <f>アイテム項目!$I214</f>
@@ -15575,7 +15588,7 @@
       </c>
       <c r="J215" t="str">
         <f>アイテム項目!$H215</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K215">
         <f>アイテム項目!$I215</f>
@@ -15667,7 +15680,7 @@
       </c>
       <c r="J217" t="str">
         <f>アイテム項目!$H217</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K217">
         <f>アイテム項目!$I217</f>
@@ -15713,7 +15726,7 @@
       </c>
       <c r="J218" t="str">
         <f>アイテム項目!$H218</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K218">
         <f>アイテム項目!$I218</f>
@@ -15759,7 +15772,7 @@
       </c>
       <c r="J219" t="str">
         <f>アイテム項目!$H219</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K219">
         <f>アイテム項目!$I219</f>
@@ -15805,7 +15818,7 @@
       </c>
       <c r="J220" t="str">
         <f>アイテム項目!$H220</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K220">
         <f>アイテム項目!$I220</f>
@@ -15851,7 +15864,7 @@
       </c>
       <c r="J221" t="str">
         <f>アイテム項目!$H221</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K221">
         <f>アイテム項目!$I221</f>
@@ -15897,7 +15910,7 @@
       </c>
       <c r="J222" t="str">
         <f>アイテム項目!$H222</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K222">
         <f>アイテム項目!$I222</f>
@@ -15943,7 +15956,7 @@
       </c>
       <c r="J223" t="str">
         <f>アイテム項目!$H223</f>
-        <v>中</v>
+        <v>A</v>
       </c>
       <c r="K223">
         <f>アイテム項目!$I223</f>
@@ -15989,7 +16002,7 @@
       </c>
       <c r="J224" t="str">
         <f>アイテム項目!$H224</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K224">
         <f>アイテム項目!$I224</f>
@@ -16035,7 +16048,7 @@
       </c>
       <c r="J225" t="str">
         <f>アイテム項目!$H225</f>
-        <v>中</v>
+        <v>A</v>
       </c>
       <c r="K225">
         <f>アイテム項目!$I225</f>
@@ -16081,7 +16094,7 @@
       </c>
       <c r="J226" t="str">
         <f>アイテム項目!$H226</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K226">
         <f>アイテム項目!$I226</f>
@@ -16127,7 +16140,7 @@
       </c>
       <c r="J227" t="str">
         <f>アイテム項目!$H227</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K227">
         <f>アイテム項目!$I227</f>
@@ -16173,7 +16186,7 @@
       </c>
       <c r="J228" t="str">
         <f>アイテム項目!$H228</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K228">
         <f>アイテム項目!$I228</f>
@@ -16219,7 +16232,7 @@
       </c>
       <c r="J229" t="str">
         <f>アイテム項目!$H229</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K229">
         <f>アイテム項目!$I229</f>
@@ -16265,7 +16278,7 @@
       </c>
       <c r="J230" t="str">
         <f>アイテム項目!$H230</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K230">
         <f>アイテム項目!$I230</f>
@@ -16311,7 +16324,7 @@
       </c>
       <c r="J231" t="str">
         <f>アイテム項目!$H231</f>
-        <v>中</v>
+        <v>A</v>
       </c>
       <c r="K231">
         <f>アイテム項目!$I231</f>
@@ -16357,7 +16370,7 @@
       </c>
       <c r="J232" t="str">
         <f>アイテム項目!$H232</f>
-        <v>中</v>
+        <v>A</v>
       </c>
       <c r="K232">
         <f>アイテム項目!$I232</f>
@@ -16403,7 +16416,7 @@
       </c>
       <c r="J233" t="str">
         <f>アイテム項目!$H233</f>
-        <v>中</v>
+        <v>A</v>
       </c>
       <c r="K233">
         <f>アイテム項目!$I233</f>
@@ -16449,7 +16462,7 @@
       </c>
       <c r="J234" t="str">
         <f>アイテム項目!$H234</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K234">
         <f>アイテム項目!$I234</f>
@@ -16495,7 +16508,7 @@
       </c>
       <c r="J235" t="str">
         <f>アイテム項目!$H235</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K235">
         <f>アイテム項目!$I235</f>
@@ -16541,7 +16554,7 @@
       </c>
       <c r="J236" t="str">
         <f>アイテム項目!$H236</f>
-        <v>高</v>
+        <v>A</v>
       </c>
       <c r="K236">
         <f>アイテム項目!$I236</f>
@@ -16587,7 +16600,7 @@
       </c>
       <c r="J237" t="str">
         <f>アイテム項目!$H237</f>
-        <v>中</v>
+        <v>A</v>
       </c>
       <c r="K237">
         <f>アイテム項目!$I237</f>
@@ -16633,7 +16646,7 @@
       </c>
       <c r="J238" t="str">
         <f>アイテム項目!$H238</f>
-        <v>低</v>
+        <v>A</v>
       </c>
       <c r="K238">
         <f>アイテム項目!$I238</f>
@@ -22889,7 +22902,7 @@
       </c>
       <c r="J374" t="str">
         <f>アイテム項目!$H374</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K374">
         <f>アイテム項目!$I374</f>
@@ -22935,7 +22948,7 @@
       </c>
       <c r="J375" t="str">
         <f>アイテム項目!$H375</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K375">
         <f>アイテム項目!$I375</f>
@@ -22981,7 +22994,7 @@
       </c>
       <c r="J376" t="str">
         <f>アイテム項目!$H376</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K376">
         <f>アイテム項目!$I376</f>
@@ -23027,7 +23040,7 @@
       </c>
       <c r="J377" t="str">
         <f>アイテム項目!$H377</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K377">
         <f>アイテム項目!$I377</f>
@@ -23073,7 +23086,7 @@
       </c>
       <c r="J378" t="str">
         <f>アイテム項目!$H378</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K378">
         <f>アイテム項目!$I378</f>
@@ -23119,7 +23132,7 @@
       </c>
       <c r="J379" t="str">
         <f>アイテム項目!$H379</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K379">
         <f>アイテム項目!$I379</f>
@@ -23165,7 +23178,7 @@
       </c>
       <c r="J380" t="str">
         <f>アイテム項目!$H380</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K380">
         <f>アイテム項目!$I380</f>
@@ -23211,7 +23224,7 @@
       </c>
       <c r="J381" t="str">
         <f>アイテム項目!$H381</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K381">
         <f>アイテム項目!$I381</f>
@@ -23257,7 +23270,7 @@
       </c>
       <c r="J382" t="str">
         <f>アイテム項目!$H382</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K382">
         <f>アイテム項目!$I382</f>
@@ -23303,7 +23316,7 @@
       </c>
       <c r="J383" t="str">
         <f>アイテム項目!$H383</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K383">
         <f>アイテム項目!$I383</f>
@@ -23349,7 +23362,7 @@
       </c>
       <c r="J384" t="str">
         <f>アイテム項目!$H384</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K384">
         <f>アイテム項目!$I384</f>
@@ -23395,7 +23408,7 @@
       </c>
       <c r="J385" t="str">
         <f>アイテム項目!$H385</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K385">
         <f>アイテム項目!$I385</f>
@@ -23441,7 +23454,7 @@
       </c>
       <c r="J386" t="str">
         <f>アイテム項目!$H386</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K386">
         <f>アイテム項目!$I386</f>
@@ -23487,7 +23500,7 @@
       </c>
       <c r="J387" t="str">
         <f>アイテム項目!$H387</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K387">
         <f>アイテム項目!$I387</f>
@@ -23533,7 +23546,7 @@
       </c>
       <c r="J388" t="str">
         <f>アイテム項目!$H388</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K388">
         <f>アイテム項目!$I388</f>
@@ -23579,7 +23592,7 @@
       </c>
       <c r="J389" t="str">
         <f>アイテム項目!$H389</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K389">
         <f>アイテム項目!$I389</f>
@@ -23625,7 +23638,7 @@
       </c>
       <c r="J390" t="str">
         <f>アイテム項目!$H390</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K390">
         <f>アイテム項目!$I390</f>
@@ -23671,7 +23684,7 @@
       </c>
       <c r="J391" t="str">
         <f>アイテム項目!$H391</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K391">
         <f>アイテム項目!$I391</f>
@@ -23717,7 +23730,7 @@
       </c>
       <c r="J392" t="str">
         <f>アイテム項目!$H392</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K392">
         <f>アイテム項目!$I392</f>
@@ -23763,7 +23776,7 @@
       </c>
       <c r="J393" t="str">
         <f>アイテム項目!$H393</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K393">
         <f>アイテム項目!$I393</f>
@@ -23809,7 +23822,7 @@
       </c>
       <c r="J394" t="str">
         <f>アイテム項目!$H394</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K394">
         <f>アイテム項目!$I394</f>
@@ -23855,7 +23868,7 @@
       </c>
       <c r="J395" t="str">
         <f>アイテム項目!$H395</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K395">
         <f>アイテム項目!$I395</f>
@@ -23901,7 +23914,7 @@
       </c>
       <c r="J396" t="str">
         <f>アイテム項目!$H396</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K396">
         <f>アイテム項目!$I396</f>
@@ -23947,7 +23960,7 @@
       </c>
       <c r="J397" t="str">
         <f>アイテム項目!$H397</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K397">
         <f>アイテム項目!$I397</f>
@@ -23993,7 +24006,7 @@
       </c>
       <c r="J398" t="str">
         <f>アイテム項目!$H398</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K398">
         <f>アイテム項目!$I398</f>
@@ -24039,7 +24052,7 @@
       </c>
       <c r="J399" t="str">
         <f>アイテム項目!$H399</f>
-        <v>C-030402</v>
+        <v>B</v>
       </c>
       <c r="K399">
         <f>アイテム項目!$I399</f>
@@ -28384,7 +28397,7 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -28394,49 +28407,49 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="B20" s="18"/>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="D22" s="18"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -28446,17 +28459,17 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -28466,47 +28479,47 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -28516,17 +28529,17 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -28536,47 +28549,47 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -28586,22 +28599,22 @@
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -28636,17 +28649,17 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C80">
         <v>175</v>
@@ -28663,12 +28676,12 @@
         <v>49</v>
       </c>
       <c r="B81" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -28702,7 +28715,7 @@
         <v>44</v>
       </c>
       <c r="B91" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -28715,7 +28728,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B93" s="18">
         <v>0.8</v>
@@ -28723,15 +28736,15 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="B94" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C95">
         <v>175</v>
@@ -28748,7 +28761,7 @@
         <v>49</v>
       </c>
       <c r="B96" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -28756,7 +28769,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -28793,7 +28806,7 @@
         <v>44</v>
       </c>
       <c r="B106" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -28803,7 +28816,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B108" s="18">
         <v>0.8</v>
@@ -28811,15 +28824,15 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="B109" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C110">
         <v>175</v>
@@ -28844,47 +28857,47 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -28894,22 +28907,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -28919,12 +28932,12 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -28934,32 +28947,32 @@
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -28969,27 +28982,27 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -29028,17 +29041,17 @@
         <v>46</v>
       </c>
       <c r="B160" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -29062,52 +29075,52 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -29122,17 +29135,17 @@
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="186" spans="1:1">
@@ -29142,7 +29155,7 @@
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="189" spans="1:1">
@@ -29152,7 +29165,7 @@
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="192" spans="1:1">
@@ -29172,22 +29185,22 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -29197,62 +29210,62 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B207" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D207" t="s">
         <v>1243</v>
-      </c>
-      <c r="B207" t="s">
-        <v>1244</v>
-      </c>
-      <c r="D207" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B209" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="B212" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B215" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
     </row>
   </sheetData>
@@ -29298,63 +29311,63 @@
     </row>
     <row r="2" spans="1:10" ht="37.5" customHeight="1">
       <c r="A2" s="33" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C2" s="33" t="s">
         <v>1256</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="D2" s="33" t="s">
         <v>1257</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="E2" s="33" t="s">
         <v>1258</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="F2" s="33" t="s">
         <v>1259</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="G2" s="33" t="s">
         <v>1260</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="H2" s="33" t="s">
         <v>1261</v>
       </c>
-      <c r="G2" s="33" t="s">
+      <c r="I2" s="33" t="s">
         <v>1262</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="J2" s="33" t="s">
         <v>1263</v>
-      </c>
-      <c r="I2" s="33" t="s">
-        <v>1264</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="56.25" customHeight="1">
       <c r="A3" s="33" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C3" s="33" t="s">
         <v>1266</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="D3" s="33" t="s">
         <v>1267</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="E3" s="33" t="s">
         <v>1268</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="F3" s="33" t="s">
+        <v>1259</v>
+      </c>
+      <c r="G3" s="33" t="s">
         <v>1269</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="H3" s="33" t="s">
         <v>1270</v>
       </c>
-      <c r="F3" s="33" t="s">
-        <v>1261</v>
-      </c>
-      <c r="G3" s="33" t="s">
+      <c r="I3" s="33" t="s">
         <v>1271</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>1272</v>
-      </c>
-      <c r="I3" s="33" t="s">
-        <v>1273</v>
       </c>
       <c r="J3" s="33" t="s">
         <v>194</v>
@@ -29362,34 +29375,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="33" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C4" s="33" t="s">
         <v>1274</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="D4" s="33" t="s">
         <v>1275</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="E4" s="33" t="s">
         <v>1276</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="F4" s="33" t="s">
         <v>1277</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="G4" s="33" t="s">
         <v>1278</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="H4" s="33" t="s">
         <v>1279</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="I4" s="33" t="s">
         <v>1280</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="J4" s="33" t="s">
         <v>1281</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>1282</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>1283</v>
       </c>
     </row>
   </sheetData>
@@ -31618,7 +31631,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="B10" t="s">
         <v>172</v>
@@ -31857,7 +31870,7 @@
         <v>249</v>
       </c>
       <c r="H24" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -32800,7 +32813,7 @@
         <v>353</v>
       </c>
       <c r="C21" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="D21" t="s">
         <v>354</v>
@@ -32861,7 +32874,7 @@
         <v>29</v>
       </c>
       <c r="H23" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -32881,10 +32894,10 @@
         <v>295</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="F28" s="29" t="s">
         <v>29</v>
@@ -32901,10 +32914,10 @@
         <v>295</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="F29" s="29" t="s">
         <v>29</v>
@@ -32921,10 +32934,10 @@
         <v>295</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="F30" s="29" t="s">
         <v>29</v>
@@ -32941,17 +32954,17 @@
         <v>295</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="F31" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G31"/>
       <c r="H31" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -32965,17 +32978,17 @@
         <v>295</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="E32" s="29" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="F32" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G32"/>
       <c r="H32" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -32989,10 +33002,10 @@
         <v>295</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="F33" s="29" t="s">
         <v>29</v>
@@ -33009,10 +33022,10 @@
         <v>295</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="F34" s="29" t="s">
         <v>29</v>
@@ -33029,10 +33042,10 @@
         <v>295</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="F35" s="29" t="s">
         <v>29</v>
@@ -33049,10 +33062,10 @@
         <v>295</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="E36" s="29" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="F36" s="29" t="s">
         <v>29</v>
@@ -33069,10 +33082,10 @@
         <v>295</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="F37" s="29" t="s">
         <v>29</v>
@@ -33089,10 +33102,10 @@
         <v>295</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="E38" s="29" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="F38" s="29" t="s">
         <v>29</v>
@@ -33109,10 +33122,10 @@
         <v>295</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="F39" s="29" t="s">
         <v>29</v>
@@ -33129,16 +33142,16 @@
         <v>295</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="E40" s="29" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="F40" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G40" s="29" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -33152,16 +33165,16 @@
         <v>295</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="F41" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G41" s="29" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -33175,16 +33188,16 @@
         <v>295</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="E42" s="29" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="F42" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G42" s="29" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -33198,16 +33211,16 @@
         <v>295</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="E43" s="29" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="F43" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G43" s="29" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -33221,16 +33234,16 @@
         <v>295</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="F44" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G44" s="29" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -33244,16 +33257,16 @@
         <v>295</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="E45" s="29" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="F45" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G45" s="29" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -33267,16 +33280,16 @@
         <v>295</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="F46" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -33290,16 +33303,16 @@
         <v>295</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="E47" s="29" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="F47" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G47" s="29" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -33313,16 +33326,16 @@
         <v>295</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="F48" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G48" s="29" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -33336,16 +33349,16 @@
         <v>295</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="F49" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G49" s="29" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -33359,16 +33372,16 @@
         <v>295</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="F50" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G50" s="29" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -33382,16 +33395,16 @@
         <v>295</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="F51" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G51" s="29" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -33405,16 +33418,16 @@
         <v>295</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="F52" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G52" s="29" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -33428,16 +33441,16 @@
         <v>295</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="F53" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G53" s="29" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -33451,16 +33464,16 @@
         <v>295</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="F54" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G54" s="29" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -33474,16 +33487,16 @@
         <v>295</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="F55" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G55" s="29" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -33497,16 +33510,16 @@
         <v>295</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="E56" s="29" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="F56" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G56" s="29" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -33520,16 +33533,16 @@
         <v>295</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="E57" s="29" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="F57" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G57" s="29" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -33543,16 +33556,16 @@
         <v>295</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E58" s="29" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="F58" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G58" s="29" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -33566,16 +33579,16 @@
         <v>295</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="E59" s="29" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G59" s="29" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -33589,16 +33602,16 @@
         <v>295</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="E60" s="29" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="F60" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G60" s="29" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -33612,16 +33625,16 @@
         <v>295</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="E61" s="29" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="F61" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G61" s="29" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -33635,16 +33648,16 @@
         <v>295</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="E62" s="29" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="F62" s="29" t="s">
         <v>29</v>
       </c>
       <c r="G62" s="29" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
   </sheetData>
@@ -33655,6 +33668,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K403"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
@@ -33698,7 +33712,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" hidden="1">
       <c r="A2" t="s">
         <v>299</v>
       </c>
@@ -33727,7 +33741,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" hidden="1">
       <c r="A3" t="s">
         <v>299</v>
       </c>
@@ -33756,7 +33770,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" hidden="1">
       <c r="A4" t="s">
         <v>299</v>
       </c>
@@ -33785,7 +33799,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" hidden="1">
       <c r="A5" t="s">
         <v>299</v>
       </c>
@@ -33814,7 +33828,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" hidden="1">
       <c r="A6" t="s">
         <v>299</v>
       </c>
@@ -33843,7 +33857,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" hidden="1">
       <c r="A7" t="s">
         <v>296</v>
       </c>
@@ -33872,7 +33886,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" hidden="1">
       <c r="A8" t="s">
         <v>296</v>
       </c>
@@ -33901,7 +33915,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" hidden="1">
       <c r="A9" t="s">
         <v>296</v>
       </c>
@@ -33930,7 +33944,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" hidden="1">
       <c r="A10" t="s">
         <v>296</v>
       </c>
@@ -33959,7 +33973,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" hidden="1">
       <c r="A11" t="s">
         <v>296</v>
       </c>
@@ -33988,7 +34002,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" hidden="1">
       <c r="A12" t="s">
         <v>296</v>
       </c>
@@ -34017,7 +34031,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" hidden="1">
       <c r="A13" t="s">
         <v>296</v>
       </c>
@@ -34046,7 +34060,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" hidden="1">
       <c r="A14" t="s">
         <v>296</v>
       </c>
@@ -34075,7 +34089,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" hidden="1">
       <c r="A15" t="s">
         <v>296</v>
       </c>
@@ -34104,7 +34118,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" hidden="1">
       <c r="A16" t="s">
         <v>296</v>
       </c>
@@ -34133,7 +34147,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" hidden="1">
       <c r="A17" t="s">
         <v>302</v>
       </c>
@@ -34162,7 +34176,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" hidden="1">
       <c r="A18" t="s">
         <v>302</v>
       </c>
@@ -34191,7 +34205,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" hidden="1">
       <c r="A19" t="s">
         <v>302</v>
       </c>
@@ -34220,7 +34234,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" hidden="1">
       <c r="A20" t="s">
         <v>302</v>
       </c>
@@ -34249,7 +34263,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" hidden="1">
       <c r="A21" t="s">
         <v>302</v>
       </c>
@@ -34278,7 +34292,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" hidden="1">
       <c r="A22" t="s">
         <v>302</v>
       </c>
@@ -34307,7 +34321,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" hidden="1">
       <c r="A23" t="s">
         <v>302</v>
       </c>
@@ -34336,7 +34350,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" hidden="1">
       <c r="A24" t="s">
         <v>302</v>
       </c>
@@ -34365,7 +34379,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" hidden="1">
       <c r="A25" t="s">
         <v>305</v>
       </c>
@@ -34394,7 +34408,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" hidden="1">
       <c r="A26" t="s">
         <v>305</v>
       </c>
@@ -34423,7 +34437,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" hidden="1">
       <c r="A27" t="s">
         <v>305</v>
       </c>
@@ -34452,7 +34466,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" hidden="1">
       <c r="A28" t="s">
         <v>305</v>
       </c>
@@ -34481,7 +34495,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" hidden="1">
       <c r="A29" t="s">
         <v>305</v>
       </c>
@@ -34510,7 +34524,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" hidden="1">
       <c r="A30" t="s">
         <v>305</v>
       </c>
@@ -34539,7 +34553,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" hidden="1">
       <c r="A31" t="s">
         <v>305</v>
       </c>
@@ -34568,7 +34582,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" hidden="1">
       <c r="A32" t="s">
         <v>305</v>
       </c>
@@ -34597,7 +34611,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" hidden="1">
       <c r="A33" t="s">
         <v>305</v>
       </c>
@@ -34626,7 +34640,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" hidden="1">
       <c r="A34" t="s">
         <v>305</v>
       </c>
@@ -34655,7 +34669,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" hidden="1">
       <c r="A35" t="s">
         <v>305</v>
       </c>
@@ -34684,7 +34698,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" hidden="1">
       <c r="A36" t="s">
         <v>305</v>
       </c>
@@ -34713,7 +34727,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" hidden="1">
       <c r="A37" t="s">
         <v>311</v>
       </c>
@@ -34742,7 +34756,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" hidden="1">
       <c r="A38" t="s">
         <v>311</v>
       </c>
@@ -34771,7 +34785,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" hidden="1">
       <c r="A39" t="s">
         <v>308</v>
       </c>
@@ -34800,7 +34814,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" hidden="1">
       <c r="A40" t="s">
         <v>308</v>
       </c>
@@ -34829,7 +34843,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" hidden="1">
       <c r="A41" t="s">
         <v>308</v>
       </c>
@@ -34858,7 +34872,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" hidden="1">
       <c r="A42" t="s">
         <v>308</v>
       </c>
@@ -34887,7 +34901,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" hidden="1">
       <c r="A43" t="s">
         <v>308</v>
       </c>
@@ -34916,7 +34930,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" hidden="1">
       <c r="A44" t="s">
         <v>308</v>
       </c>
@@ -34945,7 +34959,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" hidden="1">
       <c r="A45" t="s">
         <v>308</v>
       </c>
@@ -34974,7 +34988,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" hidden="1">
       <c r="A46" t="s">
         <v>308</v>
       </c>
@@ -35003,7 +35017,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" hidden="1">
       <c r="A47" t="s">
         <v>308</v>
       </c>
@@ -35032,7 +35046,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" hidden="1">
       <c r="A48" t="s">
         <v>308</v>
       </c>
@@ -35061,7 +35075,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" hidden="1">
       <c r="A49" t="s">
         <v>308</v>
       </c>
@@ -35090,7 +35104,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" hidden="1">
       <c r="A50" t="s">
         <v>308</v>
       </c>
@@ -35119,7 +35133,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" hidden="1">
       <c r="A51" t="s">
         <v>308</v>
       </c>
@@ -35148,7 +35162,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" hidden="1">
       <c r="A52" t="s">
         <v>308</v>
       </c>
@@ -35177,7 +35191,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" hidden="1">
       <c r="A53" t="s">
         <v>315</v>
       </c>
@@ -35206,7 +35220,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" hidden="1">
       <c r="A54" t="s">
         <v>315</v>
       </c>
@@ -35235,7 +35249,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" hidden="1">
       <c r="A55" t="s">
         <v>319</v>
       </c>
@@ -35264,7 +35278,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" hidden="1">
       <c r="A56" t="s">
         <v>319</v>
       </c>
@@ -35293,7 +35307,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" hidden="1">
       <c r="A57" t="s">
         <v>319</v>
       </c>
@@ -35322,7 +35336,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" hidden="1">
       <c r="A58" t="s">
         <v>319</v>
       </c>
@@ -35351,7 +35365,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" hidden="1">
       <c r="A59" t="s">
         <v>319</v>
       </c>
@@ -35380,7 +35394,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" hidden="1">
       <c r="A60" t="s">
         <v>319</v>
       </c>
@@ -35409,7 +35423,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" hidden="1">
       <c r="A61" t="s">
         <v>319</v>
       </c>
@@ -35438,7 +35452,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" hidden="1">
       <c r="A62" t="s">
         <v>319</v>
       </c>
@@ -35467,7 +35481,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" hidden="1">
       <c r="A63" t="s">
         <v>319</v>
       </c>
@@ -35496,7 +35510,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" hidden="1">
       <c r="A64" t="s">
         <v>319</v>
       </c>
@@ -35525,7 +35539,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" hidden="1">
       <c r="A65" t="s">
         <v>319</v>
       </c>
@@ -35554,7 +35568,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" hidden="1">
       <c r="A66" t="s">
         <v>319</v>
       </c>
@@ -35583,7 +35597,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" hidden="1">
       <c r="A67" t="s">
         <v>319</v>
       </c>
@@ -35612,7 +35626,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" hidden="1">
       <c r="A68" t="s">
         <v>211</v>
       </c>
@@ -35639,7 +35653,7 @@
       </c>
       <c r="I68"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" hidden="1">
       <c r="A69" t="s">
         <v>211</v>
       </c>
@@ -35666,7 +35680,7 @@
       </c>
       <c r="I69"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" hidden="1">
       <c r="A70" t="s">
         <v>211</v>
       </c>
@@ -35693,7 +35707,7 @@
       </c>
       <c r="I70"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" hidden="1">
       <c r="A71" t="s">
         <v>211</v>
       </c>
@@ -35720,7 +35734,7 @@
       </c>
       <c r="I71"/>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" hidden="1">
       <c r="A72" t="s">
         <v>211</v>
       </c>
@@ -35747,7 +35761,7 @@
       </c>
       <c r="I72"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" hidden="1">
       <c r="A73" t="s">
         <v>211</v>
       </c>
@@ -35774,7 +35788,7 @@
       </c>
       <c r="I73"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" hidden="1">
       <c r="A74" t="s">
         <v>211</v>
       </c>
@@ -35801,7 +35815,7 @@
       </c>
       <c r="I74"/>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" hidden="1">
       <c r="A75" t="s">
         <v>211</v>
       </c>
@@ -35828,7 +35842,7 @@
       </c>
       <c r="I75"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" hidden="1">
       <c r="A76" t="s">
         <v>211</v>
       </c>
@@ -35855,7 +35869,7 @@
       </c>
       <c r="I76"/>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" hidden="1">
       <c r="A77" t="s">
         <v>211</v>
       </c>
@@ -35882,7 +35896,7 @@
       </c>
       <c r="I77"/>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" hidden="1">
       <c r="A78" t="s">
         <v>211</v>
       </c>
@@ -35909,7 +35923,7 @@
       </c>
       <c r="I78"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" hidden="1">
       <c r="A79" t="s">
         <v>211</v>
       </c>
@@ -35936,7 +35950,7 @@
       </c>
       <c r="I79"/>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" hidden="1">
       <c r="A80" t="s">
         <v>211</v>
       </c>
@@ -35963,7 +35977,7 @@
       </c>
       <c r="I80"/>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" hidden="1">
       <c r="A81" t="s">
         <v>211</v>
       </c>
@@ -35990,7 +36004,7 @@
       </c>
       <c r="I81"/>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" hidden="1">
       <c r="A82" t="s">
         <v>211</v>
       </c>
@@ -36017,7 +36031,7 @@
       </c>
       <c r="I82"/>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" hidden="1">
       <c r="A83" t="s">
         <v>211</v>
       </c>
@@ -36044,7 +36058,7 @@
       </c>
       <c r="I83"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" hidden="1">
       <c r="A84" t="s">
         <v>350</v>
       </c>
@@ -36070,7 +36084,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" hidden="1">
       <c r="A85" t="s">
         <v>350</v>
       </c>
@@ -36096,7 +36110,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" hidden="1">
       <c r="A86" t="s">
         <v>350</v>
       </c>
@@ -36122,7 +36136,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" hidden="1">
       <c r="A87" t="s">
         <v>350</v>
       </c>
@@ -36148,7 +36162,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" hidden="1">
       <c r="A88" t="s">
         <v>350</v>
       </c>
@@ -36174,7 +36188,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" hidden="1">
       <c r="A89" t="s">
         <v>350</v>
       </c>
@@ -36200,7 +36214,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" hidden="1">
       <c r="A90" t="s">
         <v>350</v>
       </c>
@@ -36226,7 +36240,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" hidden="1">
       <c r="A91" t="s">
         <v>350</v>
       </c>
@@ -36252,7 +36266,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" hidden="1">
       <c r="A92"/>
       <c r="B92"/>
       <c r="C92"/>
@@ -36262,7 +36276,7 @@
       <c r="H92"/>
       <c r="I92"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" hidden="1">
       <c r="A93"/>
       <c r="B93"/>
       <c r="C93"/>
@@ -36272,7 +36286,7 @@
       <c r="H93"/>
       <c r="I93"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" hidden="1">
       <c r="A94"/>
       <c r="B94"/>
       <c r="C94"/>
@@ -36282,7 +36296,7 @@
       <c r="H94"/>
       <c r="I94"/>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" hidden="1">
       <c r="A95"/>
       <c r="B95"/>
       <c r="C95"/>
@@ -36292,7 +36306,7 @@
       <c r="H95"/>
       <c r="I95"/>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" hidden="1">
       <c r="A96"/>
       <c r="B96"/>
       <c r="C96"/>
@@ -36302,7 +36316,7 @@
       <c r="H96"/>
       <c r="I96"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" hidden="1">
       <c r="A97"/>
       <c r="B97"/>
       <c r="C97"/>
@@ -36312,7 +36326,7 @@
       <c r="H97"/>
       <c r="I97"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" hidden="1">
       <c r="A98"/>
       <c r="B98"/>
       <c r="C98"/>
@@ -36323,7 +36337,7 @@
       <c r="I98"/>
       <c r="J98"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" hidden="1">
       <c r="A99"/>
       <c r="B99"/>
       <c r="C99"/>
@@ -36333,7 +36347,7 @@
       <c r="H99"/>
       <c r="I99"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" hidden="1">
       <c r="A100"/>
       <c r="B100"/>
       <c r="C100"/>
@@ -36344,7 +36358,7 @@
       <c r="I100"/>
       <c r="J100"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" hidden="1">
       <c r="A101"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -36354,7 +36368,7 @@
       <c r="H101"/>
       <c r="I101"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" hidden="1">
       <c r="A102"/>
       <c r="B102"/>
       <c r="C102"/>
@@ -36364,7 +36378,7 @@
       <c r="H102"/>
       <c r="I102"/>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" hidden="1">
       <c r="A103"/>
       <c r="B103"/>
       <c r="C103"/>
@@ -36374,7 +36388,7 @@
       <c r="H103"/>
       <c r="I103"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" hidden="1">
       <c r="A104"/>
       <c r="B104"/>
       <c r="C104"/>
@@ -36384,7 +36398,7 @@
       <c r="H104"/>
       <c r="I104"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" hidden="1">
       <c r="A105"/>
       <c r="B105"/>
       <c r="C105"/>
@@ -36394,7 +36408,7 @@
       <c r="H105"/>
       <c r="I105"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" hidden="1">
       <c r="A106"/>
       <c r="B106"/>
       <c r="C106"/>
@@ -36404,7 +36418,7 @@
       <c r="H106"/>
       <c r="I106"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" hidden="1">
       <c r="A107"/>
       <c r="B107"/>
       <c r="C107"/>
@@ -36414,7 +36428,7 @@
       <c r="H107"/>
       <c r="I107"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" hidden="1">
       <c r="A108"/>
       <c r="B108"/>
       <c r="C108"/>
@@ -36425,7 +36439,7 @@
       <c r="I108"/>
       <c r="J108"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" hidden="1">
       <c r="A109"/>
       <c r="B109"/>
       <c r="C109"/>
@@ -36436,7 +36450,7 @@
       <c r="I109"/>
       <c r="J109"/>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" hidden="1">
       <c r="A110"/>
       <c r="B110"/>
       <c r="C110"/>
@@ -36446,7 +36460,7 @@
       <c r="H110"/>
       <c r="I110"/>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" hidden="1">
       <c r="A111"/>
       <c r="B111"/>
       <c r="C111"/>
@@ -36456,7 +36470,7 @@
       <c r="H111"/>
       <c r="I111"/>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" hidden="1">
       <c r="A112"/>
       <c r="B112"/>
       <c r="C112"/>
@@ -36466,7 +36480,7 @@
       <c r="H112"/>
       <c r="I112"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" hidden="1">
       <c r="A113"/>
       <c r="B113"/>
       <c r="C113"/>
@@ -36476,7 +36490,7 @@
       <c r="H113"/>
       <c r="I113"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" hidden="1">
       <c r="A114"/>
       <c r="B114"/>
       <c r="C114"/>
@@ -36486,7 +36500,7 @@
       <c r="H114"/>
       <c r="I114"/>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" hidden="1">
       <c r="A115"/>
       <c r="B115"/>
       <c r="C115"/>
@@ -36496,7 +36510,7 @@
       <c r="H115"/>
       <c r="I115"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" hidden="1">
       <c r="A116" t="s">
         <v>264</v>
       </c>
@@ -36522,7 +36536,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" hidden="1">
       <c r="A117" t="s">
         <v>264</v>
       </c>
@@ -36548,7 +36562,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" hidden="1">
       <c r="A118" t="s">
         <v>264</v>
       </c>
@@ -36574,7 +36588,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" hidden="1">
       <c r="A119" t="s">
         <v>264</v>
       </c>
@@ -36600,7 +36614,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" hidden="1">
       <c r="A120" t="s">
         <v>264</v>
       </c>
@@ -36626,7 +36640,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" hidden="1">
       <c r="A121"/>
       <c r="B121"/>
       <c r="C121"/>
@@ -36635,7 +36649,7 @@
       <c r="G121"/>
       <c r="H121"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" hidden="1">
       <c r="A122" t="s">
         <v>267</v>
       </c>
@@ -36661,7 +36675,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" hidden="1">
       <c r="A123" t="s">
         <v>267</v>
       </c>
@@ -36687,7 +36701,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" hidden="1">
       <c r="A124" t="s">
         <v>267</v>
       </c>
@@ -36713,7 +36727,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" hidden="1">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -36739,7 +36753,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" spans="1:9" hidden="1">
       <c r="A126" t="s">
         <v>267</v>
       </c>
@@ -36765,7 +36779,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" hidden="1">
       <c r="A127" t="s">
         <v>267</v>
       </c>
@@ -36791,7 +36805,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" hidden="1">
       <c r="A128" t="s">
         <v>267</v>
       </c>
@@ -36817,7 +36831,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" hidden="1">
       <c r="A129" t="s">
         <v>267</v>
       </c>
@@ -36843,7 +36857,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" hidden="1">
       <c r="A130" t="s">
         <v>267</v>
       </c>
@@ -36869,7 +36883,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" hidden="1">
       <c r="A131" t="s">
         <v>267</v>
       </c>
@@ -36895,7 +36909,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" hidden="1">
       <c r="A132" t="s">
         <v>267</v>
       </c>
@@ -36921,7 +36935,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" hidden="1">
       <c r="A133" t="s">
         <v>267</v>
       </c>
@@ -36947,7 +36961,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" hidden="1">
       <c r="A134" t="s">
         <v>267</v>
       </c>
@@ -36973,7 +36987,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" hidden="1">
       <c r="A135" t="s">
         <v>267</v>
       </c>
@@ -36999,7 +37013,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" hidden="1">
       <c r="A136" t="s">
         <v>267</v>
       </c>
@@ -37025,7 +37039,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" hidden="1">
       <c r="A137" t="s">
         <v>267</v>
       </c>
@@ -37051,7 +37065,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" hidden="1">
       <c r="A138" t="s">
         <v>267</v>
       </c>
@@ -37077,7 +37091,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" hidden="1">
       <c r="A139" t="s">
         <v>267</v>
       </c>
@@ -37103,7 +37117,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" hidden="1">
       <c r="A140" t="s">
         <v>267</v>
       </c>
@@ -37129,7 +37143,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" hidden="1">
       <c r="A141" t="s">
         <v>267</v>
       </c>
@@ -37156,7 +37170,7 @@
       </c>
       <c r="I141"/>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" hidden="1">
       <c r="A142" t="s">
         <v>267</v>
       </c>
@@ -37183,7 +37197,7 @@
       </c>
       <c r="I142"/>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" hidden="1">
       <c r="A143" t="s">
         <v>267</v>
       </c>
@@ -37209,7 +37223,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" hidden="1">
       <c r="A144" t="s">
         <v>267</v>
       </c>
@@ -37235,7 +37249,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" hidden="1">
       <c r="A145" t="s">
         <v>267</v>
       </c>
@@ -37261,7 +37275,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" hidden="1">
       <c r="A146" t="s">
         <v>267</v>
       </c>
@@ -37287,7 +37301,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" hidden="1">
       <c r="A147" t="s">
         <v>267</v>
       </c>
@@ -37313,7 +37327,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" hidden="1">
       <c r="A148" t="s">
         <v>267</v>
       </c>
@@ -37339,7 +37353,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" hidden="1">
       <c r="A149"/>
       <c r="B149"/>
       <c r="C149"/>
@@ -37348,7 +37362,7 @@
       <c r="G149"/>
       <c r="H149"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" hidden="1">
       <c r="A150" t="s">
         <v>274</v>
       </c>
@@ -37374,7 +37388,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" hidden="1">
       <c r="A151" t="s">
         <v>274</v>
       </c>
@@ -37400,7 +37414,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" hidden="1">
       <c r="A152" t="s">
         <v>274</v>
       </c>
@@ -37426,7 +37440,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" hidden="1">
       <c r="A153" t="s">
         <v>274</v>
       </c>
@@ -37452,7 +37466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" hidden="1">
       <c r="A154" t="s">
         <v>274</v>
       </c>
@@ -37478,7 +37492,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" hidden="1">
       <c r="A155" t="s">
         <v>274</v>
       </c>
@@ -37504,7 +37518,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" hidden="1">
       <c r="A156" t="s">
         <v>274</v>
       </c>
@@ -37530,7 +37544,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" hidden="1">
       <c r="A157" t="s">
         <v>274</v>
       </c>
@@ -37556,7 +37570,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" hidden="1">
       <c r="A158" t="s">
         <v>274</v>
       </c>
@@ -37582,7 +37596,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" hidden="1">
       <c r="A159" t="s">
         <v>274</v>
       </c>
@@ -37608,7 +37622,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" hidden="1">
       <c r="A160" t="s">
         <v>274</v>
       </c>
@@ -37634,7 +37648,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" hidden="1">
       <c r="A161" t="s">
         <v>274</v>
       </c>
@@ -37660,7 +37674,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" hidden="1">
       <c r="A162" t="s">
         <v>274</v>
       </c>
@@ -37686,7 +37700,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" hidden="1">
       <c r="A163" t="s">
         <v>274</v>
       </c>
@@ -37712,7 +37726,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" hidden="1">
       <c r="A164" t="s">
         <v>274</v>
       </c>
@@ -37738,7 +37752,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" hidden="1">
       <c r="A165" t="s">
         <v>274</v>
       </c>
@@ -37764,7 +37778,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" hidden="1">
       <c r="A166" t="s">
         <v>274</v>
       </c>
@@ -37790,7 +37804,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" hidden="1">
       <c r="A167" t="s">
         <v>274</v>
       </c>
@@ -37816,7 +37830,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" hidden="1">
       <c r="A168" t="s">
         <v>274</v>
       </c>
@@ -37842,7 +37856,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" hidden="1">
       <c r="A169" t="s">
         <v>274</v>
       </c>
@@ -37868,7 +37882,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" hidden="1">
       <c r="A170" t="s">
         <v>274</v>
       </c>
@@ -37894,7 +37908,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" hidden="1">
       <c r="A171" t="s">
         <v>274</v>
       </c>
@@ -37920,7 +37934,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" hidden="1">
       <c r="A172"/>
       <c r="B172"/>
       <c r="C172"/>
@@ -37929,7 +37943,7 @@
       <c r="G172"/>
       <c r="H172"/>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" hidden="1">
       <c r="A173" t="s">
         <v>270</v>
       </c>
@@ -37962,7 +37976,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" hidden="1">
       <c r="A174" t="s">
         <v>270</v>
       </c>
@@ -37989,7 +38003,7 @@
       </c>
       <c r="I174"/>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" hidden="1">
       <c r="A175" t="s">
         <v>270</v>
       </c>
@@ -38016,7 +38030,7 @@
       </c>
       <c r="I175"/>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" hidden="1">
       <c r="A176" t="s">
         <v>270</v>
       </c>
@@ -38042,7 +38056,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" hidden="1">
       <c r="A177" t="s">
         <v>270</v>
       </c>
@@ -38072,7 +38086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" hidden="1">
       <c r="A178" t="s">
         <v>270</v>
       </c>
@@ -38098,7 +38112,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" hidden="1">
       <c r="A179" t="s">
         <v>270</v>
       </c>
@@ -38124,7 +38138,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" hidden="1">
       <c r="A180" t="s">
         <v>270</v>
       </c>
@@ -38151,7 +38165,7 @@
       </c>
       <c r="I180"/>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" hidden="1">
       <c r="A181" t="s">
         <v>270</v>
       </c>
@@ -38178,7 +38192,7 @@
       </c>
       <c r="I181"/>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" hidden="1">
       <c r="A182" t="s">
         <v>270</v>
       </c>
@@ -38208,7 +38222,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" hidden="1">
       <c r="A183" t="s">
         <v>270</v>
       </c>
@@ -38241,7 +38255,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" hidden="1">
       <c r="A184" t="s">
         <v>270</v>
       </c>
@@ -38271,7 +38285,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" hidden="1">
       <c r="A185" t="s">
         <v>270</v>
       </c>
@@ -38298,7 +38312,7 @@
       </c>
       <c r="I185"/>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" hidden="1">
       <c r="A186" t="s">
         <v>270</v>
       </c>
@@ -38325,7 +38339,7 @@
       </c>
       <c r="I186"/>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" hidden="1">
       <c r="A187" t="s">
         <v>270</v>
       </c>
@@ -38351,7 +38365,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" hidden="1">
       <c r="A188" t="s">
         <v>270</v>
       </c>
@@ -38381,7 +38395,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" hidden="1">
       <c r="A189" t="s">
         <v>270</v>
       </c>
@@ -38414,7 +38428,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" hidden="1">
       <c r="A190" t="s">
         <v>270</v>
       </c>
@@ -38444,7 +38458,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" hidden="1">
       <c r="A191" t="s">
         <v>270</v>
       </c>
@@ -38471,7 +38485,7 @@
       </c>
       <c r="I191"/>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" hidden="1">
       <c r="A192" t="s">
         <v>270</v>
       </c>
@@ -38498,7 +38512,7 @@
       </c>
       <c r="I192"/>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" hidden="1">
       <c r="A193" t="s">
         <v>270</v>
       </c>
@@ -38524,7 +38538,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" hidden="1">
       <c r="A194" t="s">
         <v>270</v>
       </c>
@@ -38551,7 +38565,7 @@
       </c>
       <c r="I194"/>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" hidden="1">
       <c r="A195" t="s">
         <v>270</v>
       </c>
@@ -38578,7 +38592,7 @@
       </c>
       <c r="I195"/>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" hidden="1">
       <c r="A196" t="s">
         <v>270</v>
       </c>
@@ -38605,7 +38619,7 @@
       </c>
       <c r="I196"/>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" hidden="1">
       <c r="A197"/>
       <c r="B197"/>
       <c r="C197"/>
@@ -39076,7 +39090,7 @@
         <v>156</v>
       </c>
       <c r="H213" t="s">
-        <v>29</v>
+        <v>1482</v>
       </c>
       <c r="I213" t="s">
         <v>826</v>
@@ -39105,7 +39119,7 @@
         <v>156</v>
       </c>
       <c r="H214" t="s">
-        <v>29</v>
+        <v>1482</v>
       </c>
       <c r="I214" t="s">
         <v>826</v>
@@ -39134,11 +39148,11 @@
         <v>833</v>
       </c>
       <c r="H215" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I215"/>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" hidden="1">
       <c r="A216"/>
       <c r="B216"/>
       <c r="C216"/>
@@ -39171,7 +39185,7 @@
         <v>833</v>
       </c>
       <c r="H217" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I217"/>
     </row>
@@ -39198,7 +39212,7 @@
         <v>839</v>
       </c>
       <c r="H218" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I218"/>
     </row>
@@ -39225,7 +39239,7 @@
         <v>839</v>
       </c>
       <c r="H219" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I219"/>
     </row>
@@ -39252,7 +39266,7 @@
         <v>844</v>
       </c>
       <c r="H220" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I220"/>
     </row>
@@ -39279,7 +39293,7 @@
         <v>847</v>
       </c>
       <c r="H221" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I221"/>
     </row>
@@ -39306,7 +39320,7 @@
         <v>850</v>
       </c>
       <c r="H222" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I222"/>
     </row>
@@ -39333,7 +39347,7 @@
         <v>853</v>
       </c>
       <c r="H223" t="s">
-        <v>9</v>
+        <v>1482</v>
       </c>
       <c r="I223"/>
     </row>
@@ -39360,7 +39374,7 @@
         <v>856</v>
       </c>
       <c r="H224" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I224"/>
     </row>
@@ -39387,7 +39401,7 @@
         <v>859</v>
       </c>
       <c r="H225" t="s">
-        <v>9</v>
+        <v>1482</v>
       </c>
       <c r="I225"/>
     </row>
@@ -39414,7 +39428,7 @@
         <v>862</v>
       </c>
       <c r="H226" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I226"/>
       <c r="J226" t="s">
@@ -39444,7 +39458,7 @@
         <v>866</v>
       </c>
       <c r="H227" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I227"/>
     </row>
@@ -39471,7 +39485,7 @@
         <v>869</v>
       </c>
       <c r="H228" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I228"/>
     </row>
@@ -39498,7 +39512,7 @@
         <v>872</v>
       </c>
       <c r="H229" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I229"/>
     </row>
@@ -39525,7 +39539,7 @@
         <v>875</v>
       </c>
       <c r="H230" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I230"/>
     </row>
@@ -39552,7 +39566,7 @@
         <v>878</v>
       </c>
       <c r="H231" t="s">
-        <v>9</v>
+        <v>1482</v>
       </c>
       <c r="I231"/>
     </row>
@@ -39579,7 +39593,7 @@
         <v>881</v>
       </c>
       <c r="H232" t="s">
-        <v>9</v>
+        <v>1482</v>
       </c>
       <c r="I232"/>
     </row>
@@ -39606,7 +39620,7 @@
         <v>884</v>
       </c>
       <c r="H233" t="s">
-        <v>9</v>
+        <v>1482</v>
       </c>
       <c r="I233"/>
       <c r="J233" t="s">
@@ -39636,7 +39650,7 @@
         <v>887</v>
       </c>
       <c r="H234" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I234"/>
       <c r="J234" t="s">
@@ -39669,7 +39683,7 @@
         <v>833</v>
       </c>
       <c r="H235" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I235"/>
     </row>
@@ -39696,7 +39710,7 @@
         <v>833</v>
       </c>
       <c r="H236" t="s">
-        <v>834</v>
+        <v>1482</v>
       </c>
       <c r="I236"/>
     </row>
@@ -39723,7 +39737,7 @@
         <v>894</v>
       </c>
       <c r="H237" t="s">
-        <v>9</v>
+        <v>1482</v>
       </c>
       <c r="I237"/>
     </row>
@@ -39750,11 +39764,11 @@
         <v>897</v>
       </c>
       <c r="H238" t="s">
-        <v>153</v>
+        <v>1482</v>
       </c>
       <c r="I238"/>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" hidden="1">
       <c r="A239" t="s">
         <v>280</v>
       </c>
@@ -39786,7 +39800,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" hidden="1">
       <c r="A240" t="s">
         <v>280</v>
       </c>
@@ -39816,7 +39830,7 @@
       </c>
       <c r="J240"/>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" hidden="1">
       <c r="A241" t="s">
         <v>280</v>
       </c>
@@ -39845,7 +39859,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" hidden="1">
       <c r="A242" t="s">
         <v>280</v>
       </c>
@@ -39874,7 +39888,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" hidden="1">
       <c r="A243" t="s">
         <v>280</v>
       </c>
@@ -39903,7 +39917,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" hidden="1">
       <c r="A244" t="s">
         <v>280</v>
       </c>
@@ -39932,7 +39946,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" hidden="1">
       <c r="A245" t="s">
         <v>280</v>
       </c>
@@ -39961,7 +39975,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" hidden="1">
       <c r="A246" t="s">
         <v>280</v>
       </c>
@@ -39990,7 +40004,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" hidden="1">
       <c r="A247" t="s">
         <v>280</v>
       </c>
@@ -40019,7 +40033,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" hidden="1">
       <c r="A248" t="s">
         <v>280</v>
       </c>
@@ -40049,7 +40063,7 @@
       </c>
       <c r="J248"/>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" hidden="1">
       <c r="A249" t="s">
         <v>280</v>
       </c>
@@ -40078,7 +40092,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" hidden="1">
       <c r="A250" t="s">
         <v>280</v>
       </c>
@@ -40107,7 +40121,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" spans="1:10" hidden="1">
       <c r="A251" t="s">
         <v>280</v>
       </c>
@@ -40136,7 +40150,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" hidden="1">
       <c r="A252" t="s">
         <v>280</v>
       </c>
@@ -40165,7 +40179,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" hidden="1">
       <c r="A253" t="s">
         <v>280</v>
       </c>
@@ -40194,7 +40208,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" hidden="1">
       <c r="A254" t="s">
         <v>280</v>
       </c>
@@ -40223,7 +40237,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" hidden="1">
       <c r="A255" t="s">
         <v>280</v>
       </c>
@@ -40253,7 +40267,7 @@
       </c>
       <c r="J255"/>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" hidden="1">
       <c r="A256" t="s">
         <v>280</v>
       </c>
@@ -40282,7 +40296,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" hidden="1">
       <c r="A257" t="s">
         <v>280</v>
       </c>
@@ -40311,7 +40325,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" hidden="1">
       <c r="A258" t="s">
         <v>280</v>
       </c>
@@ -40340,7 +40354,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" hidden="1">
       <c r="A259" t="s">
         <v>280</v>
       </c>
@@ -40369,7 +40383,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" hidden="1">
       <c r="A260" t="s">
         <v>280</v>
       </c>
@@ -40398,7 +40412,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" hidden="1">
       <c r="A261" t="s">
         <v>280</v>
       </c>
@@ -40424,7 +40438,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="263" spans="1:9">
+    <row r="262" spans="1:9" hidden="1"/>
+    <row r="263" spans="1:9" hidden="1">
       <c r="A263" t="s">
         <v>224</v>
       </c>
@@ -40445,7 +40460,7 @@
       </c>
       <c r="I263"/>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" hidden="1">
       <c r="A264" t="s">
         <v>224</v>
       </c>
@@ -40466,7 +40481,7 @@
       </c>
       <c r="I264"/>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" hidden="1">
       <c r="A265" t="s">
         <v>224</v>
       </c>
@@ -40487,7 +40502,7 @@
       </c>
       <c r="I265"/>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" hidden="1">
       <c r="A266" t="s">
         <v>224</v>
       </c>
@@ -40508,7 +40523,7 @@
       </c>
       <c r="I266"/>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" hidden="1">
       <c r="A267" t="s">
         <v>224</v>
       </c>
@@ -40529,7 +40544,7 @@
       </c>
       <c r="I267"/>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" hidden="1">
       <c r="A268" t="s">
         <v>224</v>
       </c>
@@ -40550,7 +40565,7 @@
       </c>
       <c r="I268"/>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" hidden="1">
       <c r="A269" t="s">
         <v>224</v>
       </c>
@@ -40571,7 +40586,7 @@
       </c>
       <c r="I269"/>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" hidden="1">
       <c r="A270" t="s">
         <v>224</v>
       </c>
@@ -40592,14 +40607,14 @@
       </c>
       <c r="I270"/>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" hidden="1">
       <c r="A271"/>
       <c r="B271"/>
       <c r="C271"/>
       <c r="D271"/>
       <c r="F271"/>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" hidden="1">
       <c r="A272" t="s">
         <v>225</v>
       </c>
@@ -40622,7 +40637,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="273" spans="1:9">
+    <row r="273" spans="1:9" hidden="1">
       <c r="A273" t="s">
         <v>225</v>
       </c>
@@ -40645,7 +40660,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="274" spans="1:9">
+    <row r="274" spans="1:9" hidden="1">
       <c r="A274" t="s">
         <v>227</v>
       </c>
@@ -40668,7 +40683,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="275" spans="1:9">
+    <row r="275" spans="1:9" hidden="1">
       <c r="A275" t="s">
         <v>227</v>
       </c>
@@ -40688,7 +40703,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="276" spans="1:9">
+    <row r="276" spans="1:9" hidden="1">
       <c r="A276" t="s">
         <v>227</v>
       </c>
@@ -40708,7 +40723,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="277" spans="1:9">
+    <row r="277" spans="1:9" hidden="1">
       <c r="A277" t="s">
         <v>227</v>
       </c>
@@ -40731,7 +40746,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="278" spans="1:9">
+    <row r="278" spans="1:9" hidden="1">
       <c r="A278" t="s">
         <v>227</v>
       </c>
@@ -40754,7 +40769,7 @@
       <c r="H278"/>
       <c r="I278"/>
     </row>
-    <row r="279" spans="1:9">
+    <row r="279" spans="1:9" hidden="1">
       <c r="A279" t="s">
         <v>227</v>
       </c>
@@ -40777,7 +40792,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="280" spans="1:9">
+    <row r="280" spans="1:9" hidden="1">
       <c r="A280" t="s">
         <v>227</v>
       </c>
@@ -40797,7 +40812,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="281" spans="1:9">
+    <row r="281" spans="1:9" hidden="1">
       <c r="A281" t="s">
         <v>227</v>
       </c>
@@ -40820,7 +40835,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="282" spans="1:9">
+    <row r="282" spans="1:9" hidden="1">
       <c r="A282" t="s">
         <v>227</v>
       </c>
@@ -40843,7 +40858,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="283" spans="1:9">
+    <row r="283" spans="1:9" hidden="1">
       <c r="A283" t="s">
         <v>227</v>
       </c>
@@ -40866,7 +40881,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="284" spans="1:9">
+    <row r="284" spans="1:9" hidden="1">
       <c r="A284" t="s">
         <v>227</v>
       </c>
@@ -40889,7 +40904,7 @@
       <c r="H284"/>
       <c r="I284"/>
     </row>
-    <row r="285" spans="1:9">
+    <row r="285" spans="1:9" hidden="1">
       <c r="A285" t="s">
         <v>227</v>
       </c>
@@ -40909,7 +40924,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="286" spans="1:9">
+    <row r="286" spans="1:9" hidden="1">
       <c r="A286" t="s">
         <v>227</v>
       </c>
@@ -40932,7 +40947,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="287" spans="1:9">
+    <row r="287" spans="1:9" hidden="1">
       <c r="A287" t="s">
         <v>227</v>
       </c>
@@ -40952,7 +40967,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="288" spans="1:9">
+    <row r="288" spans="1:9" hidden="1">
       <c r="A288" t="s">
         <v>227</v>
       </c>
@@ -40975,7 +40990,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
+    <row r="289" spans="1:9" hidden="1">
       <c r="A289" t="s">
         <v>227</v>
       </c>
@@ -40995,14 +41010,14 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
+    <row r="290" spans="1:9" hidden="1">
       <c r="A290"/>
       <c r="B290"/>
       <c r="C290"/>
       <c r="D290"/>
       <c r="F290"/>
     </row>
-    <row r="291" spans="1:9">
+    <row r="291" spans="1:9" hidden="1">
       <c r="A291" t="s">
         <v>229</v>
       </c>
@@ -41025,7 +41040,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="292" spans="1:9">
+    <row r="292" spans="1:9" hidden="1">
       <c r="A292" t="s">
         <v>229</v>
       </c>
@@ -41048,7 +41063,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" hidden="1">
       <c r="A293" t="s">
         <v>229</v>
       </c>
@@ -41068,7 +41083,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="294" spans="1:9">
+    <row r="294" spans="1:9" hidden="1">
       <c r="A294" t="s">
         <v>229</v>
       </c>
@@ -41088,7 +41103,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="295" spans="1:9">
+    <row r="295" spans="1:9" hidden="1">
       <c r="A295" t="s">
         <v>229</v>
       </c>
@@ -41111,7 +41126,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="296" spans="1:9">
+    <row r="296" spans="1:9" hidden="1">
       <c r="A296" t="s">
         <v>229</v>
       </c>
@@ -41134,7 +41149,7 @@
       <c r="H296"/>
       <c r="I296"/>
     </row>
-    <row r="297" spans="1:9">
+    <row r="297" spans="1:9" hidden="1">
       <c r="A297" t="s">
         <v>229</v>
       </c>
@@ -41154,7 +41169,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="298" spans="1:9">
+    <row r="298" spans="1:9" hidden="1">
       <c r="A298" t="s">
         <v>229</v>
       </c>
@@ -41174,7 +41189,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="299" spans="1:9">
+    <row r="299" spans="1:9" hidden="1">
       <c r="A299" t="s">
         <v>229</v>
       </c>
@@ -41194,7 +41209,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
+    <row r="300" spans="1:9" hidden="1">
       <c r="A300" t="s">
         <v>229</v>
       </c>
@@ -41214,7 +41229,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" hidden="1">
       <c r="A301" t="s">
         <v>229</v>
       </c>
@@ -41234,7 +41249,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" hidden="1">
       <c r="A302" t="s">
         <v>229</v>
       </c>
@@ -41254,7 +41269,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="303" spans="1:9">
+    <row r="303" spans="1:9" hidden="1">
       <c r="A303" t="s">
         <v>229</v>
       </c>
@@ -41274,7 +41289,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="304" spans="1:9">
+    <row r="304" spans="1:9" hidden="1">
       <c r="A304" t="s">
         <v>229</v>
       </c>
@@ -41294,7 +41309,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="305" spans="1:9">
+    <row r="305" spans="1:9" hidden="1">
       <c r="A305" t="s">
         <v>229</v>
       </c>
@@ -41314,7 +41329,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="306" spans="1:9">
+    <row r="306" spans="1:9" hidden="1">
       <c r="A306" t="s">
         <v>229</v>
       </c>
@@ -41334,7 +41349,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="307" spans="1:9">
+    <row r="307" spans="1:9" hidden="1">
       <c r="A307" t="s">
         <v>229</v>
       </c>
@@ -41354,7 +41369,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="308" spans="1:9">
+    <row r="308" spans="1:9" hidden="1">
       <c r="A308" t="s">
         <v>229</v>
       </c>
@@ -41374,14 +41389,14 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="309" spans="1:9">
+    <row r="309" spans="1:9" hidden="1">
       <c r="A309"/>
       <c r="B309"/>
       <c r="C309"/>
       <c r="D309"/>
       <c r="F309"/>
     </row>
-    <row r="310" spans="1:9">
+    <row r="310" spans="1:9" hidden="1">
       <c r="A310" t="s">
         <v>231</v>
       </c>
@@ -41404,7 +41419,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="311" spans="1:9">
+    <row r="311" spans="1:9" hidden="1">
       <c r="A311" t="s">
         <v>231</v>
       </c>
@@ -41427,7 +41442,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="312" spans="1:9">
+    <row r="312" spans="1:9" hidden="1">
       <c r="A312" t="s">
         <v>231</v>
       </c>
@@ -41450,7 +41465,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="313" spans="1:9">
+    <row r="313" spans="1:9" hidden="1">
       <c r="A313" t="s">
         <v>231</v>
       </c>
@@ -41473,7 +41488,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="314" spans="1:9">
+    <row r="314" spans="1:9" hidden="1">
       <c r="A314" t="s">
         <v>231</v>
       </c>
@@ -41496,7 +41511,7 @@
       <c r="H314"/>
       <c r="I314"/>
     </row>
-    <row r="315" spans="1:9">
+    <row r="315" spans="1:9" hidden="1">
       <c r="A315" t="s">
         <v>231</v>
       </c>
@@ -41519,7 +41534,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="316" spans="1:9">
+    <row r="316" spans="1:9" hidden="1">
       <c r="A316" t="s">
         <v>231</v>
       </c>
@@ -41542,7 +41557,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="317" spans="1:9">
+    <row r="317" spans="1:9" hidden="1">
       <c r="A317" t="s">
         <v>231</v>
       </c>
@@ -41565,7 +41580,7 @@
       <c r="H317"/>
       <c r="I317"/>
     </row>
-    <row r="318" spans="1:9">
+    <row r="318" spans="1:9" hidden="1">
       <c r="A318" t="s">
         <v>231</v>
       </c>
@@ -41588,7 +41603,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="319" spans="1:9">
+    <row r="319" spans="1:9" hidden="1">
       <c r="A319" t="s">
         <v>231</v>
       </c>
@@ -41611,7 +41626,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="320" spans="1:9">
+    <row r="320" spans="1:9" hidden="1">
       <c r="A320" t="s">
         <v>231</v>
       </c>
@@ -41634,7 +41649,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="321" spans="1:9">
+    <row r="321" spans="1:9" hidden="1">
       <c r="A321" t="s">
         <v>231</v>
       </c>
@@ -41657,7 +41672,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="322" spans="1:9">
+    <row r="322" spans="1:9" hidden="1">
       <c r="A322" t="s">
         <v>231</v>
       </c>
@@ -41680,7 +41695,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="323" spans="1:9">
+    <row r="323" spans="1:9" hidden="1">
       <c r="A323" t="s">
         <v>231</v>
       </c>
@@ -41703,7 +41718,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="324" spans="1:9">
+    <row r="324" spans="1:9" hidden="1">
       <c r="A324" t="s">
         <v>231</v>
       </c>
@@ -41723,7 +41738,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="325" spans="1:9">
+    <row r="325" spans="1:9" hidden="1">
       <c r="A325" t="s">
         <v>231</v>
       </c>
@@ -41746,14 +41761,14 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="326" spans="1:9">
+    <row r="326" spans="1:9" hidden="1">
       <c r="A326"/>
       <c r="B326"/>
       <c r="C326"/>
       <c r="D326"/>
       <c r="F326"/>
     </row>
-    <row r="327" spans="1:9">
+    <row r="327" spans="1:9" hidden="1">
       <c r="A327" t="s">
         <v>286</v>
       </c>
@@ -41776,7 +41791,7 @@
       <c r="H327"/>
       <c r="I327"/>
     </row>
-    <row r="328" spans="1:9">
+    <row r="328" spans="1:9" hidden="1">
       <c r="A328" t="s">
         <v>286</v>
       </c>
@@ -41799,7 +41814,7 @@
       <c r="H328"/>
       <c r="I328"/>
     </row>
-    <row r="329" spans="1:9">
+    <row r="329" spans="1:9" hidden="1">
       <c r="A329" t="s">
         <v>286</v>
       </c>
@@ -41822,7 +41837,7 @@
       <c r="H329"/>
       <c r="I329"/>
     </row>
-    <row r="330" spans="1:9">
+    <row r="330" spans="1:9" hidden="1">
       <c r="A330" t="s">
         <v>286</v>
       </c>
@@ -41845,7 +41860,7 @@
       <c r="H330"/>
       <c r="I330"/>
     </row>
-    <row r="331" spans="1:9">
+    <row r="331" spans="1:9" hidden="1">
       <c r="A331" t="s">
         <v>286</v>
       </c>
@@ -41868,7 +41883,7 @@
       <c r="H331"/>
       <c r="I331"/>
     </row>
-    <row r="332" spans="1:9">
+    <row r="332" spans="1:9" hidden="1">
       <c r="A332" t="s">
         <v>286</v>
       </c>
@@ -41891,7 +41906,7 @@
       <c r="H332"/>
       <c r="I332"/>
     </row>
-    <row r="333" spans="1:9">
+    <row r="333" spans="1:9" hidden="1">
       <c r="A333" t="s">
         <v>286</v>
       </c>
@@ -41911,7 +41926,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="334" spans="1:9">
+    <row r="334" spans="1:9" hidden="1">
       <c r="A334" t="s">
         <v>286</v>
       </c>
@@ -41934,7 +41949,7 @@
       <c r="H334"/>
       <c r="I334"/>
     </row>
-    <row r="335" spans="1:9">
+    <row r="335" spans="1:9" hidden="1">
       <c r="A335" t="s">
         <v>286</v>
       </c>
@@ -41957,7 +41972,7 @@
       <c r="H335"/>
       <c r="I335"/>
     </row>
-    <row r="336" spans="1:9">
+    <row r="336" spans="1:9" hidden="1">
       <c r="A336" t="s">
         <v>286</v>
       </c>
@@ -41980,7 +41995,7 @@
       <c r="H336"/>
       <c r="I336"/>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" hidden="1">
       <c r="A337" t="s">
         <v>286</v>
       </c>
@@ -42003,7 +42018,7 @@
       <c r="H337"/>
       <c r="I337"/>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" hidden="1">
       <c r="A338" t="s">
         <v>286</v>
       </c>
@@ -42026,7 +42041,7 @@
       <c r="H338"/>
       <c r="I338"/>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" hidden="1">
       <c r="A339" t="s">
         <v>286</v>
       </c>
@@ -42049,7 +42064,7 @@
       <c r="H339"/>
       <c r="I339"/>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" hidden="1">
       <c r="A340" t="s">
         <v>286</v>
       </c>
@@ -42072,7 +42087,8 @@
       <c r="H340"/>
       <c r="I340"/>
     </row>
-    <row r="342" spans="1:10">
+    <row r="341" spans="1:10" hidden="1"/>
+    <row r="342" spans="1:10" hidden="1">
       <c r="A342" t="s">
         <v>359</v>
       </c>
@@ -42095,7 +42111,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" hidden="1">
       <c r="A343" t="s">
         <v>359</v>
       </c>
@@ -42118,7 +42134,7 @@
       <c r="H343"/>
       <c r="I343"/>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" hidden="1">
       <c r="A344" t="s">
         <v>359</v>
       </c>
@@ -42141,7 +42157,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" hidden="1">
       <c r="A345" t="s">
         <v>359</v>
       </c>
@@ -42161,7 +42177,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" hidden="1">
       <c r="A346" t="s">
         <v>359</v>
       </c>
@@ -42184,7 +42200,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" hidden="1">
       <c r="A347" t="s">
         <v>277</v>
       </c>
@@ -42214,7 +42230,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" hidden="1">
       <c r="A348" t="s">
         <v>277</v>
       </c>
@@ -42241,24 +42257,26 @@
       </c>
       <c r="I348"/>
     </row>
-    <row r="351" spans="1:10">
+    <row r="349" spans="1:10" hidden="1"/>
+    <row r="350" spans="1:10" hidden="1"/>
+    <row r="351" spans="1:10" hidden="1">
       <c r="A351" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B351" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C351" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D351" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E351" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="F351" s="29" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="G351" s="29" t="s">
         <v>156</v>
@@ -42267,24 +42285,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" hidden="1">
       <c r="A352" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B352" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C352" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D352" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E352" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="F352" s="29" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="G352" s="29" t="s">
         <v>156</v>
@@ -42293,24 +42311,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="353" spans="1:8">
+    <row r="353" spans="1:8" hidden="1">
       <c r="A353" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B353" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C353" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D353" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E353" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="F353" s="29" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="G353" s="29" t="s">
         <v>156</v>
@@ -42319,24 +42337,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="354" spans="1:8">
+    <row r="354" spans="1:8" hidden="1">
       <c r="A354" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B354" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C354" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D354" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E354" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="F354" s="29" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="G354" s="29" t="s">
         <v>156</v>
@@ -42345,24 +42363,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="355" spans="1:8">
+    <row r="355" spans="1:8" hidden="1">
       <c r="A355" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B355" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C355" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D355" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E355" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="F355" s="29" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="G355" s="29" t="s">
         <v>156</v>
@@ -42371,24 +42389,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="356" spans="1:8">
+    <row r="356" spans="1:8" hidden="1">
       <c r="A356" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B356" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C356" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D356" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E356" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="F356" s="29" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="G356" s="29" t="s">
         <v>156</v>
@@ -42397,24 +42415,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="357" spans="1:8">
+    <row r="357" spans="1:8" hidden="1">
       <c r="A357" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B357" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C357" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D357" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E357" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="F357" s="29" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="G357" s="29" t="s">
         <v>156</v>
@@ -42423,24 +42441,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="358" spans="1:8">
+    <row r="358" spans="1:8" hidden="1">
       <c r="A358" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B358" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C358" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D358" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E358" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="F358" s="29" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="G358" s="29" t="s">
         <v>156</v>
@@ -42449,24 +42467,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="359" spans="1:8">
+    <row r="359" spans="1:8" hidden="1">
       <c r="A359" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B359" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C359" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D359" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E359" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="F359" s="29" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="G359" s="29" t="s">
         <v>156</v>
@@ -42475,24 +42493,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="360" spans="1:8">
+    <row r="360" spans="1:8" hidden="1">
       <c r="A360" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B360" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C360" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D360" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E360" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="F360" s="29" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="G360" s="29" t="s">
         <v>156</v>
@@ -42501,24 +42519,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="361" spans="1:8">
+    <row r="361" spans="1:8" hidden="1">
       <c r="A361" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B361" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C361" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D361" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E361" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="F361" s="29" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="G361" s="29" t="s">
         <v>156</v>
@@ -42527,24 +42545,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="362" spans="1:8">
+    <row r="362" spans="1:8" hidden="1">
       <c r="A362" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B362" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C362" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D362" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E362" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="F362" s="29" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="G362" s="29" t="s">
         <v>156</v>
@@ -42553,24 +42571,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="363" spans="1:8">
+    <row r="363" spans="1:8" hidden="1">
       <c r="A363" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B363" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C363" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D363" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E363" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="F363" s="29" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="G363" s="29" t="s">
         <v>156</v>
@@ -42579,24 +42597,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="364" spans="1:8">
+    <row r="364" spans="1:8" hidden="1">
       <c r="A364" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B364" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C364" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D364" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E364" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="F364" s="29" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="G364" s="29" t="s">
         <v>156</v>
@@ -42605,24 +42623,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="365" spans="1:8">
+    <row r="365" spans="1:8" hidden="1">
       <c r="A365" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B365" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C365" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D365" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E365" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="F365" s="29" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="G365" s="29" t="s">
         <v>156</v>
@@ -42631,24 +42649,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="366" spans="1:8">
+    <row r="366" spans="1:8" hidden="1">
       <c r="A366" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B366" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C366" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D366" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E366" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="F366" s="29" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="G366" s="29" t="s">
         <v>156</v>
@@ -42657,24 +42675,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="367" spans="1:8">
+    <row r="367" spans="1:8" hidden="1">
       <c r="A367" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B367" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C367" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D367" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E367" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="F367" s="29" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="G367" s="29" t="s">
         <v>156</v>
@@ -42683,24 +42701,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="368" spans="1:8">
+    <row r="368" spans="1:8" hidden="1">
       <c r="A368" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B368" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C368" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D368" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E368" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="F368" s="29" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="G368" s="29" t="s">
         <v>156</v>
@@ -42709,24 +42727,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="369" spans="1:8">
+    <row r="369" spans="1:8" hidden="1">
       <c r="A369" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B369" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C369" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D369" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E369" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="F369" s="29" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="G369" s="29" t="s">
         <v>156</v>
@@ -42735,24 +42753,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="370" spans="1:8">
+    <row r="370" spans="1:8" hidden="1">
       <c r="A370" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B370" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C370" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D370" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E370" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F370" s="29" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G370" s="29" t="s">
         <v>156</v>
@@ -42761,24 +42779,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="371" spans="1:8">
+    <row r="371" spans="1:8" hidden="1">
       <c r="A371" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B371" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C371" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D371" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E371" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="F371" s="29" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="G371" s="29" t="s">
         <v>156</v>
@@ -42787,24 +42805,24 @@
         <v>29</v>
       </c>
     </row>
-    <row r="372" spans="1:8">
+    <row r="372" spans="1:8" hidden="1">
       <c r="A372" s="29" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B372" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C372" s="29" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D372" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E372" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="F372" s="29" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="G372" s="29" t="s">
         <v>156</v>
@@ -42813,700 +42831,701 @@
         <v>29</v>
       </c>
     </row>
-    <row r="374" spans="1:8">
+    <row r="373" spans="1:8" hidden="1"/>
+    <row r="374" spans="1:8" hidden="1">
       <c r="A374" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B374" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C374" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D374" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E374" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="F374" s="29" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="G374" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H374" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="375" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" hidden="1">
       <c r="A375" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B375" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C375" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D375" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E375" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="F375" s="29" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="G375" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H375" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="376" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" hidden="1">
       <c r="A376" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B376" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C376" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D376" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E376" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="F376" s="29" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G376" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H376" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="377" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" hidden="1">
       <c r="A377" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B377" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C377" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D377" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E377" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="F377" s="29" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="G377" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H377" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="378" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" hidden="1">
       <c r="A378" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B378" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C378" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D378" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E378" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="F378" s="29" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="G378" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H378" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="379" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" hidden="1">
       <c r="A379" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B379" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C379" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D379" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E379" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="F379" s="29" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="G379" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H379" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="380" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" hidden="1">
       <c r="A380" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B380" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C380" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D380" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E380" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="F380" s="29" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="G380" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H380" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="381" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" hidden="1">
       <c r="A381" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B381" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C381" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D381" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E381" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="F381" s="29" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="G381" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H381" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="382" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" hidden="1">
       <c r="A382" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B382" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C382" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D382" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E382" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="F382" s="29" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="G382" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H382" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="383" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" hidden="1">
       <c r="A383" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B383" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C383" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D383" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E383" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="F383" s="29" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="G383" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H383" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="384" spans="1:8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" hidden="1">
       <c r="A384" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B384" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C384" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D384" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E384" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="F384" s="29" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G384" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H384" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="385" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" hidden="1">
       <c r="A385" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B385" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C385" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D385" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E385" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="F385" s="29" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="G385" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H385" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="386" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" hidden="1">
       <c r="A386" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B386" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C386" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D386" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E386" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="F386" s="29" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="G386" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H386" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="387" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" hidden="1">
       <c r="A387" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B387" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C387" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D387" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E387" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F387" s="29" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="G387" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H387" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="388" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" hidden="1">
       <c r="A388" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B388" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C388" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D388" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E388" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="F388" s="29" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="G388" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H388" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="389" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" hidden="1">
       <c r="A389" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B389" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C389" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D389" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E389" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="F389" s="29" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="G389" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H389" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="390" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" hidden="1">
       <c r="A390" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B390" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C390" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D390" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E390" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="F390" s="29" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="G390" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H390" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="391" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" hidden="1">
       <c r="A391" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B391" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C391" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D391" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E391" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="F391" s="29" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="G391" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H391" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="392" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" hidden="1">
       <c r="A392" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B392" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C392" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D392" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E392" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="F392" s="29" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="G392" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H392" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="393" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" hidden="1">
       <c r="A393" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B393" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C393" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D393" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E393" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="F393" s="29" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="G393" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H393" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="394" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" hidden="1">
       <c r="A394" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B394" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C394" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D394" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E394" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="F394" s="29" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G394" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H394" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="395" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" hidden="1">
       <c r="A395" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B395" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C395" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D395" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E395" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="F395" s="29" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="G395" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H395" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="396" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" hidden="1">
       <c r="A396" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B396" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C396" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D396" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E396" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="F396" s="29" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="G396" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H396" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="397" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" hidden="1">
       <c r="A397" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B397" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C397" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D397" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E397" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="F397" s="29" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="G397" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H397" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="398" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" hidden="1">
       <c r="A398" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B398" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C398" s="29" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D398" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E398" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="F398" s="29" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="G398" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H398" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="399" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" hidden="1">
       <c r="A399" s="29" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B399" s="29" t="s">
-        <v>295</v>
+        <v>1481</v>
       </c>
       <c r="C399" s="29" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="D399" s="29" t="s">
         <v>156</v>
       </c>
       <c r="E399" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="F399" s="29" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="G399" s="29" t="s">
         <v>156</v>
       </c>
       <c r="H399" s="29" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="400" spans="1:9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" hidden="1">
       <c r="A400" s="29" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="B400" s="29" t="s">
         <v>53</v>
       </c>
       <c r="C400" s="29" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="D400" s="29" t="s">
         <v>147</v>
       </c>
       <c r="E400" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="F400" s="29" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="G400" s="29" t="s">
         <v>147</v>
@@ -43515,32 +43534,40 @@
         <v>29</v>
       </c>
       <c r="I400" s="29" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" hidden="1"/>
+    <row r="402" spans="1:6" hidden="1">
+      <c r="A402" s="29" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C402" s="29" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E402" t="s">
         <v>1474</v>
       </c>
-    </row>
-    <row r="402" spans="1:6">
-      <c r="A402" s="29" t="s">
-        <v>1477</v>
-      </c>
-      <c r="C402" s="29" t="s">
-        <v>1479</v>
-      </c>
-      <c r="E402" t="s">
+      <c r="F402" s="29" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" hidden="1">
+      <c r="C403" s="29" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F403" s="29" t="s">
         <v>1476</v>
       </c>
-      <c r="F402" s="29" t="s">
-        <v>1475</v>
-      </c>
-    </row>
-    <row r="403" spans="1:6">
-      <c r="C403" s="29" t="s">
-        <v>1480</v>
-      </c>
-      <c r="F403" s="29" t="s">
-        <v>1478</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A403" xr:uid="{00000000-0001-0000-0700-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="C-040201"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -43593,7 +43620,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>1150</v>
+        <v>1479</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -43602,27 +43629,27 @@
         <v>324</v>
       </c>
       <c r="D2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="E2" t="s">
         <v>1140</v>
       </c>
       <c r="F2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H2" t="s">
         <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1154</v>
+        <v>1480</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -43631,22 +43658,22 @@
         <v>328</v>
       </c>
       <c r="D3" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="E3" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="F3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H3" t="s">
         <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
   </sheetData>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Documents\Codex\2026-09-14\copilot-chatgpt-c-c-t-id\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91A2F09-0DA7-4DA0-A239-C04AEAA6E5A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ED1095-8C08-44E2-B8D8-802ED7F15A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1200" yWindow="1035" windowWidth="26385" windowHeight="13440" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4170" uniqueCount="1483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4170" uniqueCount="1484">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -4013,9 +4013,6 @@
   </si>
   <si>
     <t>内部未調査</t>
-  </si>
-  <si>
-    <t>C-010506</t>
   </si>
   <si>
     <t>N-00002</t>
@@ -4482,6 +4479,14 @@
   </si>
   <si>
     <t>有効</t>
+  </si>
+  <si>
+    <t>C-010504</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="15"/>
   </si>
 </sst>
 </file>
@@ -5844,8 +5849,8 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>1327</v>
+      <c r="A3" s="19" t="s">
+        <v>1482</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -5854,10 +5859,10 @@
         <v>307</v>
       </c>
       <c r="D3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E3" t="s">
         <v>1328</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1329</v>
       </c>
       <c r="F3" t="s">
         <v>1325</v>
@@ -5892,22 +5897,22 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B1" t="s">
         <v>1330</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1331</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1332</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1333</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1334</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1335</v>
       </c>
       <c r="G1" t="s">
         <v>433</v>
@@ -16130,7 +16135,7 @@
       </c>
       <c r="J223" t="str">
         <f>アイテム項目!$H223</f>
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="K223">
         <f>アイテム項目!$I223</f>
@@ -16222,7 +16227,7 @@
       </c>
       <c r="J225" t="str">
         <f>アイテム項目!$H225</f>
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="K225">
         <f>アイテム項目!$I225</f>
@@ -16498,7 +16503,7 @@
       </c>
       <c r="J231" t="str">
         <f>アイテム項目!$H231</f>
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="K231">
         <f>アイテム項目!$I231</f>
@@ -16544,7 +16549,7 @@
       </c>
       <c r="J232" t="str">
         <f>アイテム項目!$H232</f>
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="K232">
         <f>アイテム項目!$I232</f>
@@ -16590,7 +16595,7 @@
       </c>
       <c r="J233" t="str">
         <f>アイテム項目!$H233</f>
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="K233">
         <f>アイテム項目!$I233</f>
@@ -16774,7 +16779,7 @@
       </c>
       <c r="J237" t="str">
         <f>アイテム項目!$H237</f>
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="K237">
         <f>アイテム項目!$I237</f>
@@ -16820,7 +16825,7 @@
       </c>
       <c r="J238" t="str">
         <f>アイテム項目!$H238</f>
-        <v>A</v>
+        <v>C</v>
       </c>
       <c r="K238">
         <f>アイテム項目!$I238</f>
@@ -28570,7 +28575,7 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -28580,49 +28585,49 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B20" s="18"/>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="D22" s="18"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -28632,17 +28637,17 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -28652,47 +28657,47 @@
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -28702,17 +28707,17 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -28722,47 +28727,47 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -28772,22 +28777,22 @@
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -28822,17 +28827,17 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C80">
         <v>175</v>
@@ -28849,12 +28854,12 @@
         <v>49</v>
       </c>
       <c r="B81" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -28888,7 +28893,7 @@
         <v>44</v>
       </c>
       <c r="B91" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -28901,7 +28906,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B93" s="18">
         <v>0.8</v>
@@ -28909,15 +28914,15 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B94" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C95">
         <v>175</v>
@@ -28934,7 +28939,7 @@
         <v>49</v>
       </c>
       <c r="B96" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -28942,7 +28947,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -28979,7 +28984,7 @@
         <v>44</v>
       </c>
       <c r="B106" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -28989,7 +28994,7 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B108" s="18">
         <v>0.8</v>
@@ -28997,15 +29002,15 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B109" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C110">
         <v>175</v>
@@ -29030,47 +29035,47 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="126" spans="1:1">
@@ -29080,22 +29085,22 @@
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -29105,12 +29110,12 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="138" spans="1:1">
@@ -29120,32 +29125,32 @@
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -29155,27 +29160,27 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -29214,17 +29219,17 @@
         <v>46</v>
       </c>
       <c r="B160" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -29248,52 +29253,52 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -29308,17 +29313,17 @@
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="186" spans="1:1">
@@ -29328,7 +29333,7 @@
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="189" spans="1:1">
@@ -29338,7 +29343,7 @@
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="192" spans="1:1">
@@ -29358,22 +29363,22 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -29383,62 +29388,62 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B207" t="s">
         <v>1422</v>
       </c>
-      <c r="B207" t="s">
+      <c r="D207" t="s">
         <v>1423</v>
-      </c>
-      <c r="D207" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B209" t="s">
         <v>1426</v>
-      </c>
-      <c r="B209" t="s">
-        <v>1427</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B212" t="s">
         <v>1429</v>
-      </c>
-      <c r="B212" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B215" t="s">
         <v>1432</v>
-      </c>
-      <c r="B215" t="s">
-        <v>1433</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
   </sheetData>
@@ -29484,63 +29489,63 @@
     </row>
     <row r="2" spans="1:10" ht="37.5" customHeight="1">
       <c r="A2" s="31" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>1435</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="C2" s="31" t="s">
         <v>1436</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="D2" s="31" t="s">
         <v>1437</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="E2" s="31" t="s">
         <v>1438</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="F2" s="31" t="s">
         <v>1439</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="G2" s="31" t="s">
         <v>1440</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="H2" s="31" t="s">
         <v>1441</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="I2" s="31" t="s">
         <v>1442</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="J2" s="31" t="s">
         <v>1443</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="56.25" customHeight="1">
       <c r="A3" s="31" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B3" s="31" t="s">
         <v>1445</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="C3" s="31" t="s">
         <v>1446</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="D3" s="31" t="s">
         <v>1447</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="E3" s="31" t="s">
         <v>1448</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="F3" s="31" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>1449</v>
       </c>
-      <c r="F3" s="31" t="s">
-        <v>1440</v>
-      </c>
-      <c r="G3" s="31" t="s">
+      <c r="H3" s="31" t="s">
         <v>1450</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="I3" s="31" t="s">
         <v>1451</v>
-      </c>
-      <c r="I3" s="31" t="s">
-        <v>1452</v>
       </c>
       <c r="J3" s="31" t="s">
         <v>437</v>
@@ -29548,34 +29553,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="31" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>1453</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="C4" s="31" t="s">
         <v>1454</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="D4" s="31" t="s">
         <v>1455</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="E4" s="31" t="s">
         <v>1456</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="F4" s="31" t="s">
         <v>1457</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="G4" s="31" t="s">
         <v>1458</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="H4" s="31" t="s">
         <v>1459</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="I4" s="31" t="s">
         <v>1460</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="J4" s="31" t="s">
         <v>1461</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>1462</v>
       </c>
     </row>
   </sheetData>
@@ -31415,19 +31420,19 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B1" t="s">
         <v>1330</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1331</v>
       </c>
       <c r="C1" t="s">
         <v>432</v>
       </c>
       <c r="D1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E1" t="s">
         <v>1332</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1333</v>
       </c>
       <c r="F1" t="s">
         <v>435</v>
@@ -31621,25 +31626,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="75" customHeight="1">
       <c r="A1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B1" t="s">
         <v>1330</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1331</v>
       </c>
       <c r="C1" t="s">
         <v>432</v>
       </c>
       <c r="D1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E1" t="s">
         <v>1332</v>
       </c>
-      <c r="E1" t="s">
-        <v>1333</v>
-      </c>
       <c r="F1" s="28" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1" s="28" t="s">
         <v>1463</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>1464</v>
       </c>
       <c r="H1" t="s">
         <v>437</v>
@@ -32475,16 +32480,16 @@
         <v>432</v>
       </c>
       <c r="D1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E1" t="s">
         <v>1334</v>
       </c>
-      <c r="E1" t="s">
-        <v>1335</v>
-      </c>
       <c r="F1" s="28" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G1" s="28" t="s">
         <v>1463</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>1464</v>
       </c>
       <c r="H1" t="s">
         <v>437</v>
@@ -33866,7 +33871,7 @@
   <sheetData>
     <row r="1" spans="1:27">
       <c r="A1" s="35" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -33880,12 +33885,12 @@
       <c r="K1" s="35"/>
       <c r="L1" s="35"/>
       <c r="N1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" s="36" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -33901,19 +33906,19 @@
     </row>
     <row r="4" spans="1:27">
       <c r="A4" s="37" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B4" s="37" t="s">
         <v>1471</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="C4" s="37" t="s">
         <v>1472</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="D4" s="37" t="s">
         <v>1473</v>
       </c>
-      <c r="D4" s="37" t="s">
-        <v>1474</v>
-      </c>
       <c r="E4" s="37" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="F4" s="37" t="s">
         <v>434</v>
@@ -33931,10 +33936,10 @@
         <v>437</v>
       </c>
       <c r="K4" s="37" t="s">
+        <v>1464</v>
+      </c>
+      <c r="L4" s="37" t="s">
         <v>1465</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>1466</v>
       </c>
       <c r="N4" s="37" t="s">
         <v>429</v>
@@ -33964,19 +33969,19 @@
         <v>437</v>
       </c>
       <c r="W4" s="37" t="s">
+        <v>1474</v>
+      </c>
+      <c r="X4" s="37" t="s">
         <v>1475</v>
       </c>
-      <c r="X4" s="37" t="s">
+      <c r="Y4" s="37" t="s">
+        <v>1464</v>
+      </c>
+      <c r="Z4" s="37" t="s">
+        <v>1465</v>
+      </c>
+      <c r="AA4" s="37" t="s">
         <v>1476</v>
-      </c>
-      <c r="Y4" s="37" t="s">
-        <v>1465</v>
-      </c>
-      <c r="Z4" s="37" t="s">
-        <v>1466</v>
-      </c>
-      <c r="AA4" s="37" t="s">
-        <v>1477</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -35689,13 +35694,13 @@
         <v>437</v>
       </c>
       <c r="L1" s="32" t="s">
+        <v>1464</v>
+      </c>
+      <c r="M1" s="32" t="s">
         <v>1465</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="N1" s="32" t="s">
         <v>1466</v>
-      </c>
-      <c r="N1" s="32" t="s">
-        <v>1467</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -42658,8 +42663,8 @@
       <c r="G223" t="s">
         <v>924</v>
       </c>
-      <c r="H223" t="s">
-        <v>17</v>
+      <c r="H223" s="19" t="s">
+        <v>1483</v>
       </c>
       <c r="I223"/>
       <c r="L223" s="33"/>
@@ -42724,8 +42729,8 @@
       <c r="G225" t="s">
         <v>930</v>
       </c>
-      <c r="H225" t="s">
-        <v>17</v>
+      <c r="H225" s="19" t="s">
+        <v>1483</v>
       </c>
       <c r="I225"/>
       <c r="L225" s="33"/>
@@ -42925,8 +42930,8 @@
       <c r="G231" t="s">
         <v>949</v>
       </c>
-      <c r="H231" t="s">
-        <v>17</v>
+      <c r="H231" s="19" t="s">
+        <v>1483</v>
       </c>
       <c r="I231"/>
       <c r="L231" s="33"/>
@@ -42958,8 +42963,8 @@
       <c r="G232" t="s">
         <v>952</v>
       </c>
-      <c r="H232" t="s">
-        <v>17</v>
+      <c r="H232" s="19" t="s">
+        <v>1483</v>
       </c>
       <c r="I232"/>
       <c r="L232" s="33"/>
@@ -42991,8 +42996,8 @@
       <c r="G233" t="s">
         <v>955</v>
       </c>
-      <c r="H233" t="s">
-        <v>17</v>
+      <c r="H233" s="19" t="s">
+        <v>1483</v>
       </c>
       <c r="I233"/>
       <c r="J233" t="s">
@@ -43132,8 +43137,8 @@
       <c r="G237" t="s">
         <v>966</v>
       </c>
-      <c r="H237" t="s">
-        <v>17</v>
+      <c r="H237" s="19" t="s">
+        <v>1483</v>
       </c>
       <c r="I237"/>
       <c r="L237" s="33"/>
@@ -43165,8 +43170,8 @@
       <c r="G238" t="s">
         <v>969</v>
       </c>
-      <c r="H238" t="s">
-        <v>17</v>
+      <c r="H238" s="19" t="s">
+        <v>1483</v>
       </c>
       <c r="I238"/>
       <c r="L238" s="33"/>
@@ -47964,24 +47969,24 @@
         <v>156</v>
       </c>
       <c r="E403" s="44" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="F403" s="44" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="G403" s="44" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H403" s="44" t="s">
         <v>29</v>
       </c>
       <c r="I403" s="44" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="J403" s="44"/>
       <c r="K403" s="44"/>
       <c r="L403" s="44" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="M403" s="45">
         <v>46279.872410416669</v>
@@ -52768,7 +52773,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="15"/>
-  <conditionalFormatting sqref="A2:N402 A405:N1000 A403:B403 D403:N403 A404:E404 G404:N404">
+  <conditionalFormatting sqref="A2:N402 A403:B403 D403:N403 A404:E404 G404:N404 A405:N1000">
     <cfRule type="expression" dxfId="6" priority="1">
       <formula>$L2="取消／欠番"</formula>
     </cfRule>

--- a/整理用001.xlsx
+++ b/整理用001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AI\washitsu-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ED1095-8C08-44E2-B8D8-802ED7F15A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0931A25-A502-40E9-83A7-8C95871E197D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="1035" windowWidth="26385" windowHeight="13440" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="1035" windowWidth="26385" windowHeight="13440" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="作業部屋見取り図" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4170" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4170" uniqueCount="1485">
   <si>
     <t>https://www.photo-pick.com/online/5L4HGxBe.link</t>
   </si>
@@ -4486,6 +4486,10 @@
   </si>
   <si>
     <t>C</t>
+    <phoneticPr fontId="15"/>
+  </si>
+  <si>
+    <t>E</t>
     <phoneticPr fontId="15"/>
   </si>
 </sst>
@@ -16825,7 +16829,7 @@
       </c>
       <c r="J238" t="str">
         <f>アイテム項目!$H238</f>
-        <v>C</v>
+        <v>E</v>
       </c>
       <c r="K238">
         <f>アイテム項目!$I238</f>
@@ -43171,7 +43175,7 @@
         <v>969</v>
       </c>
       <c r="H238" s="19" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="I238"/>
       <c r="L238" s="33"/>
